--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -498,10 +498,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="28.83203125"/>
     <col min="2" max="2" customWidth="1" width="30.83203125"/>
+    <col min="3" max="3" customWidth="1" width="30.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,10 +512,13 @@
       <c r="B1" t="str">
         <v>Website</v>
       </c>
+      <c r="C1" t="str">
+        <v>Logo</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -681,7 +685,7 @@
         <v xml:space="preserve">  Photo</v>
       </c>
       <c r="B7" t="str">
-        <v>An image link, or leave it to the app (it stores a small picture here when you add one).</v>
+        <v>An image link, or use 'Add photo' in the app (it stores a small picture here). LinkedIn exports don't include photos.</v>
       </c>
     </row>
     <row r="8">
@@ -721,7 +725,7 @@
         <v>Targets</v>
       </c>
       <c r="B12" t="str">
-        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer / Closed) are optional.</v>
+        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
       </c>
     </row>
     <row r="13">
@@ -729,7 +733,7 @@
         <v>Companies</v>
       </c>
       <c r="B13" t="str">
-        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong.</v>
+        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong, or put an image link in Logo.</v>
       </c>
     </row>
     <row r="14">

--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="16.83203125"/>
     <col min="2" max="2" customWidth="1" width="30.83203125"/>
@@ -590,9 +590,17 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Avatar style</v>
+      </c>
+      <c r="B3" t="str">
+        <v>initials</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -626,7 +634,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -746,23 +754,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Layout / Settings</v>
+        <v>Settings</v>
       </c>
       <c r="B15" t="str">
-        <v>Managed by the app (saved node positions, your name).</v>
+        <v>Your name, and Avatar style: initials, or notionists for illustrated avatars drawn in your browser.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>Privacy</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B17" t="str">
         <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -669,7 +669,7 @@
         <v xml:space="preserve">  Company / School</v>
       </c>
       <c r="B4" t="str">
-        <v>3+ direct connections at one company or school become a group bubble. 'BYU' and 'Brigham Young University' count as the same.</v>
+        <v>3+ direct connections at one company or school become a group bubble. 'Stanford' and 'Stanford University' count as the same.</v>
       </c>
     </row>
     <row r="5">

--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -7,9 +7,11 @@
     <sheet name="Targets" sheetId="2" r:id="rId2"/>
     <sheet name="Companies" sheetId="3" r:id="rId3"/>
     <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
-    <sheet name="Settings" sheetId="5" r:id="rId5"/>
-    <sheet name="Layout" sheetId="6" r:id="rId6" state="hidden"/>
-    <sheet name="How to use" sheetId="7" r:id="rId7"/>
+    <sheet name="Meetings" sheetId="5" r:id="rId5"/>
+    <sheet name="Tasks" sheetId="6" r:id="rId6"/>
+    <sheet name="Settings" sheetId="7" r:id="rId7"/>
+    <sheet name="Layout" sheetId="8" r:id="rId8" state="hidden"/>
+    <sheet name="How to use" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -568,10 +570,116 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:K1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16.83203125"/>
-    <col min="2" max="2" customWidth="1" width="30.83203125"/>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="12.83203125"/>
+    <col min="3" max="3" customWidth="1" width="8.83203125"/>
+    <col min="4" max="4" customWidth="1" width="8.83203125"/>
+    <col min="5" max="5" customWidth="1" width="16.83203125"/>
+    <col min="6" max="6" customWidth="1" width="12.83203125"/>
+    <col min="7" max="7" customWidth="1" width="40.83203125"/>
+    <col min="8" max="8" customWidth="1" width="30.83203125"/>
+    <col min="9" max="9" customWidth="1" width="22.83203125"/>
+    <col min="10" max="10" customWidth="1" width="30.83203125"/>
+    <col min="11" max="11" customWidth="1" width="16.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Start</v>
+      </c>
+      <c r="D1" t="str">
+        <v>End</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Method</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Next Step</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Calendar Event ID</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Link</v>
+      </c>
+      <c r="K1" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="40.83203125"/>
+    <col min="2" max="2" customWidth="1" width="22.83203125"/>
+    <col min="3" max="3" customWidth="1" width="20.83203125"/>
+    <col min="4" max="4" customWidth="1" width="12.83203125"/>
+    <col min="5" max="5" customWidth="1" width="8.83203125"/>
+    <col min="6" max="6" customWidth="1" width="12.83203125"/>
+    <col min="7" max="7" customWidth="1" width="20.83203125"/>
+    <col min="8" max="8" customWidth="1" width="16.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Task</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Person</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Company</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Due</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Done</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Created</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Source</v>
+      </c>
+      <c r="H1" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="26.83203125"/>
+    <col min="2" max="2" customWidth="1" width="60.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,14 +706,62 @@
         <v>initials</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Your email</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Meeting length (minutes)</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Zoom link</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Check-in every (days)</v>
+      </c>
+      <c r="B7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Invite message</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Demo base date</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C1"/>
   <cols>
@@ -632,9 +788,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -754,31 +910,47 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Settings</v>
+        <v>Meetings</v>
       </c>
       <c r="B15" t="str">
-        <v>Your name, and Avatar style: initials, or notionists for illustrated avatars drawn in your browser.</v>
+        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Layout</v>
+        <v>Tasks</v>
       </c>
       <c r="B16" t="str">
-        <v>Managed by the app (saved node positions).</v>
+        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>Privacy</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B19" t="str">
         <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -406,11 +406,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="22.83203125"/>
     <col min="2" max="2" customWidth="1" width="24.83203125"/>
-    <col min="3" max="3" customWidth="1" width="24.83203125"/>
+    <col min="3" max="3" customWidth="1" width="30.83203125"/>
     <col min="4" max="4" customWidth="1" width="24.83203125"/>
     <col min="5" max="5" customWidth="1" width="28.83203125"/>
     <col min="6" max="6" customWidth="1" width="36.83203125"/>
@@ -420,6 +420,7 @@
     <col min="10" max="10" customWidth="1" width="14.83203125"/>
     <col min="11" max="11" customWidth="1" width="20.83203125"/>
     <col min="12" max="12" customWidth="1" width="40.83203125"/>
+    <col min="13" max="13" customWidth="1" width="36.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,7 +431,7 @@
         <v>Company</v>
       </c>
       <c r="C1" t="str">
-        <v>School</v>
+        <v>Schools</v>
       </c>
       <c r="D1" t="str">
         <v>Role</v>
@@ -459,10 +460,13 @@
       <c r="L1" t="str">
         <v>Notes</v>
       </c>
+      <c r="M1" t="str">
+        <v>Past Companies</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -9,9 +9,10 @@
     <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
     <sheet name="Meetings" sheetId="5" r:id="rId5"/>
     <sheet name="Tasks" sheetId="6" r:id="rId6"/>
-    <sheet name="Settings" sheetId="7" r:id="rId7"/>
-    <sheet name="Layout" sheetId="8" r:id="rId8" state="hidden"/>
-    <sheet name="How to use" sheetId="9" r:id="rId9"/>
+    <sheet name="Me" sheetId="7" r:id="rId7"/>
+    <sheet name="Settings" sheetId="8" r:id="rId8"/>
+    <sheet name="Layout" sheetId="9" r:id="rId9" state="hidden"/>
+    <sheet name="How to use" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -471,6 +472,173 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B19"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="110.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet / column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>What to put there</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>People</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Everyone on your map. Only Name is required.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">  Name</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Full name, spelled the same way everywhere.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">  Company / School</v>
+      </c>
+      <c r="B4" t="str">
+        <v>3+ direct connections at one company or school become a group bubble. 'Stanford' and 'Stanford University' count as the same.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">  Email</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Shown in the details panel with a copy button.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">  LinkedIn URL</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Their profile link. Double-click them on the map to open it.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve">  Photo</v>
+      </c>
+      <c r="B7" t="str">
+        <v>An image link, or use 'Add photo' in the app (it stores a small picture here). LinkedIn exports don't include photos.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">  Connected Through</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Leave BLANK if you know them directly. Otherwise put the name of the person who connects you; they appear as a 2nd-degree connection.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">  Connected On</v>
+      </c>
+      <c r="B9" t="str">
+        <v>The date you connected (filled in from LinkedIn).</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">  Status</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Met / Contacted / To Reach Out / Follow Up / Referral.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">  Tags, Notes</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Anything you want to remember. Tags are comma-separated.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Targets</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Companies</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong, or put an image link in Logo.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LinkedIn Pool</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Filled by 'Import LinkedIn' from your Connections.csv. These people are NOT on the map until you add them.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Meetings</v>
+      </c>
+      <c r="B15" t="str">
+        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Privacy</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
@@ -680,6 +848,117 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="70.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Role</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Headline</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Schools</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Past Companies</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Email</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LinkedIn URL</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Location</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>What I'm looking for</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="26.83203125"/>
@@ -765,7 +1044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C1"/>
   <cols>
@@ -790,171 +1069,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="110.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Sheet / column</v>
-      </c>
-      <c r="B1" t="str">
-        <v>What to put there</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>People</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Everyone on your map. Only Name is required.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v xml:space="preserve">  Name</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Full name, spelled the same way everywhere.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">  Company / School</v>
-      </c>
-      <c r="B4" t="str">
-        <v>3+ direct connections at one company or school become a group bubble. 'Stanford' and 'Stanford University' count as the same.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">  Email</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Shown in the details panel with a copy button.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">  LinkedIn URL</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Their profile link. Double-click them on the map to open it.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">  Photo</v>
-      </c>
-      <c r="B7" t="str">
-        <v>An image link, or use 'Add photo' in the app (it stores a small picture here). LinkedIn exports don't include photos.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">  Connected Through</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Leave BLANK if you know them directly. Otherwise put the name of the person who connects you; they appear as a 2nd-degree connection.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v xml:space="preserve">  Connected On</v>
-      </c>
-      <c r="B9" t="str">
-        <v>The date you connected (filled in from LinkedIn).</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">  Status</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Met / Contacted / To Reach Out / Follow Up / Referral.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v xml:space="preserve">  Tags, Notes</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Anything you want to remember. Tags are comma-separated.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Targets</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Companies</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong, or put an image link in Logo.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>LinkedIn Pool</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Filled by 'Import LinkedIn' from your Connections.csv. These people are NOT on the map until you add them.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Meetings</v>
-      </c>
-      <c r="B15" t="str">
-        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Tasks</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Settings</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Layout</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Managed by the app (saved node positions).</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Privacy</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -9,10 +9,11 @@
     <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
     <sheet name="Meetings" sheetId="5" r:id="rId5"/>
     <sheet name="Tasks" sheetId="6" r:id="rId6"/>
-    <sheet name="Me" sheetId="7" r:id="rId7"/>
-    <sheet name="Settings" sheetId="8" r:id="rId8"/>
-    <sheet name="Layout" sheetId="9" r:id="rId9" state="hidden"/>
-    <sheet name="How to use" sheetId="10" r:id="rId10"/>
+    <sheet name="Connections" sheetId="7" r:id="rId7"/>
+    <sheet name="Me" sheetId="8" r:id="rId8"/>
+    <sheet name="Settings" sheetId="9" r:id="rId9"/>
+    <sheet name="Layout" sheetId="10" r:id="rId10" state="hidden"/>
+    <sheet name="How to use" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -474,7 +475,34 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:C1"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="36.83203125"/>
+    <col min="2" max="2" customWidth="1" width="8.83203125"/>
+    <col min="3" max="3" customWidth="1" width="8.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Node</v>
+      </c>
+      <c r="B1" t="str">
+        <v>X</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B21"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -594,47 +622,63 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Meetings</v>
+        <v>Connections</v>
       </c>
       <c r="B15" t="str">
-        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
+        <v>Who knows whom: Person A, Person B, Type (Introduced me, Coworker, Classmate, Friend, Mentor, or anything else), Notes. 'Introduced me' means A introduced you to B; it's kept in sync with People → Connected Through.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Tasks</v>
+        <v>Me</v>
       </c>
       <c r="B16" t="str">
-        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
+        <v>Your own profile: photo, role, schools, past companies, what you're looking for.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Settings</v>
+        <v>Meetings</v>
       </c>
       <c r="B17" t="str">
-        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Layout</v>
+        <v>Tasks</v>
       </c>
       <c r="B18" t="str">
-        <v>Managed by the app (saved node positions).</v>
+        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
         <v>Privacy</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B21" t="str">
         <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -848,6 +892,37 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D1"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="24.83203125"/>
+    <col min="2" max="2" customWidth="1" width="24.83203125"/>
+    <col min="3" max="3" customWidth="1" width="16.83203125"/>
+    <col min="4" max="4" customWidth="1" width="40.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Person A</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Person B</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B12"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="22.83203125"/>
@@ -957,7 +1032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
   <cols>
@@ -1042,31 +1117,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="36.83203125"/>
-    <col min="2" max="2" customWidth="1" width="8.83203125"/>
-    <col min="3" max="3" customWidth="1" width="8.83203125"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Node</v>
-      </c>
-      <c r="B1" t="str">
-        <v>X</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -673,7 +673,7 @@
         <v>Privacy</v>
       </c>
       <c r="B21" t="str">
-        <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
+        <v>Orbit runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>

--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -4,16 +4,18 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="People" sheetId="1" r:id="rId1"/>
-    <sheet name="Targets" sheetId="2" r:id="rId2"/>
-    <sheet name="Companies" sheetId="3" r:id="rId3"/>
-    <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
-    <sheet name="Meetings" sheetId="5" r:id="rId5"/>
-    <sheet name="Tasks" sheetId="6" r:id="rId6"/>
-    <sheet name="Connections" sheetId="7" r:id="rId7"/>
-    <sheet name="Me" sheetId="8" r:id="rId8"/>
-    <sheet name="Settings" sheetId="9" r:id="rId9"/>
-    <sheet name="Layout" sheetId="10" r:id="rId10" state="hidden"/>
-    <sheet name="How to use" sheetId="11" r:id="rId11"/>
+    <sheet name="How to use" sheetId="2" r:id="rId2"/>
+    <sheet name="Targets" sheetId="3" r:id="rId3"/>
+    <sheet name="Companies" sheetId="4" r:id="rId4"/>
+    <sheet name="LinkedIn Pool" sheetId="5" r:id="rId5"/>
+    <sheet name="Meetings" sheetId="6" r:id="rId6"/>
+    <sheet name="Tasks" sheetId="7" r:id="rId7"/>
+    <sheet name="Connections" sheetId="8" r:id="rId8"/>
+    <sheet name="Experience" sheetId="9" r:id="rId9"/>
+    <sheet name="Education" sheetId="10" r:id="rId10"/>
+    <sheet name="Me" sheetId="11" r:id="rId11"/>
+    <sheet name="Settings" sheetId="12" r:id="rId12"/>
+    <sheet name="Layout" sheetId="13" r:id="rId13" state="hidden"/>
   </sheets>
 </workbook>
 </file>
@@ -46,8 +48,16 @@
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -75,8 +85,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,78 +424,352 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:U1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="22.83203125"/>
-    <col min="2" max="2" customWidth="1" width="24.83203125"/>
-    <col min="3" max="3" customWidth="1" width="30.83203125"/>
-    <col min="4" max="4" customWidth="1" width="24.83203125"/>
-    <col min="5" max="5" customWidth="1" width="28.83203125"/>
-    <col min="6" max="6" customWidth="1" width="36.83203125"/>
-    <col min="7" max="7" customWidth="1" width="14.83203125"/>
-    <col min="8" max="8" customWidth="1" width="22.83203125"/>
-    <col min="9" max="9" customWidth="1" width="14.83203125"/>
-    <col min="10" max="10" customWidth="1" width="14.83203125"/>
-    <col min="11" max="11" customWidth="1" width="20.83203125"/>
-    <col min="12" max="12" customWidth="1" width="40.83203125"/>
-    <col min="13" max="13" customWidth="1" width="36.83203125"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" customWidth="1"/>
+    <col min="18" max="18" width="11.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="20" max="20" width="8.83203125" customWidth="1"/>
+    <col min="21" max="21" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="1">
         <v>Name</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="1">
         <v>Company</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="1">
         <v>Schools</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="1">
         <v>Role</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="1">
         <v>Email</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="1">
         <v>LinkedIn URL</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="1">
         <v>Photo</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" t="str" s="1">
         <v>Connected Through</v>
       </c>
-      <c r="I1" t="str">
+      <c r="I1" t="str" s="1">
         <v>Connected On</v>
       </c>
-      <c r="J1" t="str">
+      <c r="J1" t="str" s="1">
         <v>Status</v>
       </c>
-      <c r="K1" t="str">
+      <c r="K1" t="str" s="1">
         <v>Tags</v>
       </c>
-      <c r="L1" t="str">
+      <c r="L1" t="str" s="1">
         <v>Notes</v>
       </c>
-      <c r="M1" t="str">
+      <c r="M1" t="str" s="1">
         <v>Past Companies</v>
+      </c>
+      <c r="N1" t="str" s="1">
+        <v>Headline</v>
+      </c>
+      <c r="O1" t="str" s="1">
+        <v>Location</v>
+      </c>
+      <c r="P1" t="str" s="1">
+        <v>Website</v>
+      </c>
+      <c r="Q1" t="str" s="1">
+        <v>Skills</v>
+      </c>
+      <c r="R1" t="str" s="1">
+        <v>Languages</v>
+      </c>
+      <c r="S1" t="str" s="1">
+        <v>Certifications</v>
+      </c>
+      <c r="T1" t="str" s="1">
+        <v>Honors</v>
+      </c>
+      <c r="U1" t="str" s="1">
+        <v>About</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="J2:J1000">
+      <formula1>"To Reach Out,Contacted,Scheduled,Met,Follow Up,Referral"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="1">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str" s="1">
+        <v>School</v>
+      </c>
+      <c r="C1" t="str" s="1">
+        <v>Degree</v>
+      </c>
+      <c r="D1" t="str" s="1">
+        <v>Field</v>
+      </c>
+      <c r="E1" t="str" s="1">
+        <v>Start</v>
+      </c>
+      <c r="F1" t="str" s="1">
+        <v>End</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="1">
+        <v>Field</v>
+      </c>
+      <c r="B1" t="str" s="1">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B2" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B3" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Role</v>
+      </c>
+      <c r="B4" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Headline</v>
+      </c>
+      <c r="B5" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B6" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Schools</v>
+      </c>
+      <c r="B7" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Past Companies</v>
+      </c>
+      <c r="B8" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Email</v>
+      </c>
+      <c r="B9" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LinkedIn URL</v>
+      </c>
+      <c r="B10" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Location</v>
+      </c>
+      <c r="B11" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>What I'm looking for</v>
+      </c>
+      <c r="B12" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="1">
+        <v>Setting</v>
+      </c>
+      <c r="B1" t="str" s="1">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Your name</v>
+      </c>
+      <c r="B2" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Avatar style</v>
+      </c>
+      <c r="B3" t="str" s="2">
+        <v>initials</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Your email</v>
+      </c>
+      <c r="B4" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Meeting length (minutes)</v>
+      </c>
+      <c r="B5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Zoom link</v>
+      </c>
+      <c r="B6" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Check-in every (days)</v>
+      </c>
+      <c r="B7" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Invite message</v>
+      </c>
+      <c r="B8" t="str" s="2">
+        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Demo base date</v>
+      </c>
+      <c r="B9" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="36.83203125"/>
-    <col min="2" max="2" customWidth="1" width="8.83203125"/>
-    <col min="3" max="3" customWidth="1" width="8.83203125"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,12 +790,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B21"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="110.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="110.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,54 +973,62 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="28.83203125"/>
-    <col min="2" max="2" customWidth="1" width="10.83203125"/>
-    <col min="3" max="3" customWidth="1" width="14.83203125"/>
-    <col min="4" max="4" customWidth="1" width="40.83203125"/>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="1">
         <v>Company</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="1">
         <v>Priority</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="1">
         <v>Stage</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="1">
         <v>Notes</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="B2:B1000">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
+      <formula1>"Researching,Networking,Applied,Interviewing,Offer"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="28.83203125"/>
-    <col min="2" max="2" customWidth="1" width="30.83203125"/>
-    <col min="3" max="3" customWidth="1" width="30.83203125"/>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="1">
         <v>Company</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="1">
         <v>Website</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="1">
         <v>Logo</v>
       </c>
     </row>
@@ -741,39 +1039,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="14.83203125"/>
-    <col min="2" max="2" customWidth="1" width="16.83203125"/>
-    <col min="3" max="3" customWidth="1" width="40.83203125"/>
-    <col min="4" max="4" customWidth="1" width="28.83203125"/>
-    <col min="5" max="5" customWidth="1" width="28.83203125"/>
-    <col min="6" max="6" customWidth="1" width="30.83203125"/>
-    <col min="7" max="7" customWidth="1" width="14.83203125"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="1">
         <v>First Name</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="1">
         <v>Last Name</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="1">
         <v>URL</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="1">
         <v>Email Address</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="1">
         <v>Company</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="1">
         <v>Position</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="1">
         <v>Connected On</v>
       </c>
     </row>
@@ -784,337 +1082,200 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="22.83203125"/>
-    <col min="2" max="2" customWidth="1" width="12.83203125"/>
-    <col min="3" max="3" customWidth="1" width="8.83203125"/>
-    <col min="4" max="4" customWidth="1" width="8.83203125"/>
-    <col min="5" max="5" customWidth="1" width="16.83203125"/>
-    <col min="6" max="6" customWidth="1" width="12.83203125"/>
-    <col min="7" max="7" customWidth="1" width="40.83203125"/>
-    <col min="8" max="8" customWidth="1" width="30.83203125"/>
-    <col min="9" max="9" customWidth="1" width="22.83203125"/>
-    <col min="10" max="10" customWidth="1" width="30.83203125"/>
-    <col min="11" max="11" customWidth="1" width="16.83203125"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="1">
         <v>Person</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="1">
         <v>Date</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="1">
         <v>Start</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="1">
         <v>End</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="1">
         <v>Type</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="1">
         <v>Method</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="1">
         <v>Notes</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" t="str" s="1">
         <v>Next Step</v>
       </c>
-      <c r="I1" t="str">
+      <c r="I1" t="str" s="1">
         <v>Calendar Event ID</v>
       </c>
-      <c r="J1" t="str">
+      <c r="J1" t="str" s="1">
         <v>Link</v>
       </c>
-      <c r="K1" t="str">
+      <c r="K1" t="str" s="1">
         <v>ID</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="E2:E1000">
+      <formula1>"Coffee Chat,Informational,Networking Event,Class/Club,Interview,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="F2:F1000">
+      <formula1>"Zoom,Google Meet,Teams,Phone,In Person,Email,LinkedIn"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40.83203125"/>
-    <col min="2" max="2" customWidth="1" width="22.83203125"/>
-    <col min="3" max="3" customWidth="1" width="20.83203125"/>
-    <col min="4" max="4" customWidth="1" width="12.83203125"/>
-    <col min="5" max="5" customWidth="1" width="8.83203125"/>
-    <col min="6" max="6" customWidth="1" width="12.83203125"/>
-    <col min="7" max="7" customWidth="1" width="20.83203125"/>
-    <col min="8" max="8" customWidth="1" width="16.83203125"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="1">
         <v>Task</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="1">
         <v>Person</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="1">
         <v>Company</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="1">
         <v>Due</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="1">
         <v>Done</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="1">
         <v>Created</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="1">
         <v>Source</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" t="str" s="1">
         <v>ID</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="E2:E1000">
+      <formula1>"Yes"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="24.83203125"/>
-    <col min="2" max="2" customWidth="1" width="24.83203125"/>
-    <col min="3" max="3" customWidth="1" width="16.83203125"/>
-    <col min="4" max="4" customWidth="1" width="40.83203125"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="1">
         <v>Person A</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="1">
         <v>Person B</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="1">
         <v>Type</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="1">
         <v>Notes</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
+      <formula1>"Introduced me,Coworker,Classmate,Friend,Mentor,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:G1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="22.83203125"/>
-    <col min="2" max="2" customWidth="1" width="70.83203125"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Field</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Photo</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Role</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Headline</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+      <c r="A1" t="str" s="1">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str" s="1">
         <v>Company</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Schools</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Past Companies</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Email</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>LinkedIn URL</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
+      <c r="C1" t="str" s="1">
+        <v>Title</v>
+      </c>
+      <c r="D1" t="str" s="1">
+        <v>Start</v>
+      </c>
+      <c r="E1" t="str" s="1">
+        <v>End</v>
+      </c>
+      <c r="F1" t="str" s="1">
         <v>Location</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>What I'm looking for</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="G1" t="str" s="1">
+        <v>Description</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="26.83203125"/>
-    <col min="2" max="2" customWidth="1" width="60.83203125"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Setting</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Your name</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Avatar style</v>
-      </c>
-      <c r="B3" t="str">
-        <v>initials</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Your email</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Meeting length (minutes)</v>
-      </c>
-      <c r="B5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Zoom link</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Check-in every (days)</v>
-      </c>
-      <c r="B7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Invite message</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Demo base date</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -678,7 +678,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -750,15 +750,23 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>Group size (people)</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>Demo base date</v>
       </c>
-      <c r="B9" t="str" s="2">
+      <c r="B10" t="str" s="2">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1084,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:Q1"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -1097,6 +1105,12 @@
     <col min="9" max="9" width="19.83203125" customWidth="1"/>
     <col min="10" max="10" width="8.83203125" customWidth="1"/>
     <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" customWidth="1"/>
+    <col min="17" max="17" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1132,6 +1146,24 @@
       </c>
       <c r="K1" t="str" s="1">
         <v>ID</v>
+      </c>
+      <c r="L1" t="str" s="1">
+        <v>Title</v>
+      </c>
+      <c r="M1" t="str" s="1">
+        <v>Guests</v>
+      </c>
+      <c r="N1" t="str" s="1">
+        <v>Location</v>
+      </c>
+      <c r="O1" t="str" s="1">
+        <v>Description</v>
+      </c>
+      <c r="P1" t="str" s="1">
+        <v>Reminder (min)</v>
+      </c>
+      <c r="Q1" t="str" s="1">
+        <v>Time Zone</v>
       </c>
     </row>
   </sheetData>
@@ -1144,7 +1176,7 @@
     </dataValidation>
   </dataValidations>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -678,7 +678,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -758,15 +758,23 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>Group by</v>
+      </c>
+      <c r="B10" t="str" s="2">
+        <v>company, school</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Demo base date</v>
       </c>
-      <c r="B10" t="str" s="2">
+      <c r="B11" t="str" s="2">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/site/template/contacts_template.xlsx
+++ b/site/template/contacts_template.xlsx
@@ -567,7 +567,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B18"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -669,9 +669,57 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>About</v>
+      </c>
+      <c r="B13" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Industry</v>
+      </c>
+      <c r="B14" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Websites</v>
+      </c>
+      <c r="B15" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Skills</v>
+      </c>
+      <c r="B16" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Certifications</v>
+      </c>
+      <c r="B17" t="str" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Volunteering</v>
+      </c>
+      <c r="B18" t="str" s="2">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1057,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:M1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -1066,6 +1114,12 @@
     <col min="5" max="5" width="9.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,10 +1144,28 @@
       <c r="G1" t="str" s="1">
         <v>Connected On</v>
       </c>
+      <c r="H1" t="str" s="1">
+        <v>Reached Out</v>
+      </c>
+      <c r="I1" t="str" s="1">
+        <v>Invited On</v>
+      </c>
+      <c r="J1" t="str" s="1">
+        <v>Invite Note</v>
+      </c>
+      <c r="K1" t="str" s="1">
+        <v>LinkedIn Note</v>
+      </c>
+      <c r="L1" t="str" s="1">
+        <v>Messages</v>
+      </c>
+      <c r="M1" t="str" s="1">
+        <v>Last Contacted</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M1"/>
   </ignoredErrors>
 </worksheet>
 </file>
